--- a/NTu/aggregate_Kipsigis_results.xlsx
+++ b/NTu/aggregate_Kipsigis_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +417,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Tea</t>
         </is>
@@ -440,202 +428,202 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>51.0745030357478</v>
+        <v>34.40052838278151</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>26.81470673897185</v>
+        <v>18.02293083448231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16.80183372065211</v>
+        <v>11.23477422464107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11.43574078072676</v>
+        <v>7.57655672150258</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.477441174861667</v>
+        <v>5.543635458910255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6.782521501186693</v>
+        <v>4.366393313592241</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5.757754937691341</v>
+        <v>3.645415483456266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5.092967058969009</v>
+        <v>3.171507276828459</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4.625032743197271</v>
+        <v>2.834378668000298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4.267740423903679</v>
+        <v>2.575526718620031</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3.975272892194776</v>
+        <v>2.363683287942768</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3.723086037508774</v>
+        <v>2.181948318645217</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3.497864634960327</v>
+        <v>2.021024428024745</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3.292235814511779</v>
+        <v>1.875652117498926</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3.101982873611642</v>
+        <v>1.742728508014423</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2.924575179747043</v>
+        <v>1.620313039471607</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2.758391499500865</v>
+        <v>1.50710095550717</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2.602308940989758</v>
+        <v>1.40214369765323</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2.455484788303617</v>
+        <v>1.304699729453565</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2.317240174322999</v>
+        <v>1.214154330875137</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2.186997571519484</v>
+        <v>1.129975919535615</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2.064246765870303</v>
+        <v>1.051691764397011</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.948525941814239</v>
+        <v>0.9788740373778447</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.839410816199399</v>
+        <v>0.9111314138621083</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1.736508088380073</v>
+        <v>0.8481036856134713</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1.639451230658101</v>
+        <v>0.7894580395936401</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.547897570920017</v>
+        <v>0.7348862851780827</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1.461526109355712</v>
+        <v>0.6841026449961541</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1.380035770241001</v>
+        <v>0.636841900904102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1.303143926929785</v>
+        <v>0.5928577801775864</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.230585111000319</v>
+        <v>0.5519215168814023</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1.16210985524877</v>
+        <v>0.5138205501124702</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.097483641001932</v>
+        <v>0.4783573352878061</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.036485931463285</v>
+        <v>0.445348252626791</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.9789092789772459</v>
+        <v>0.4146226014595129</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.9245584975932127</v>
+        <v>0.3860216716504397</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.8732498943393736</v>
+        <v>0.3593978850307262</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.8248105538774553</v>
+        <v>0.3346140008223178</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.7790776720367774</v>
+        <v>0.3115423797893773</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.7358979342914628</v>
+        <v>0.2900643024143743</v>
       </c>
     </row>
   </sheetData>
